--- a/engineer_reporting_organizations/Organization Schema.xlsx
+++ b/engineer_reporting_organizations/Organization Schema.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rdcrlbpm/Applications/usace-master-data/engineer_reporting_organizations/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADD54ABB-0603-D341-8562-C47803BCE7AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6658F250-993F-9E4A-BCF7-4617C84C0997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1240" windowWidth="54280" windowHeight="28200" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1300" yWindow="600" windowWidth="49900" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Data Dictionary" sheetId="1" r:id="rId1"/>
@@ -50,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="532">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="533">
   <si>
     <t>Table</t>
   </si>
@@ -1054,9 +1054,6 @@
     <t>N2</t>
   </si>
   <si>
-    <t>TED</t>
-  </si>
-  <si>
     <t>CETED</t>
   </si>
   <si>
@@ -1066,19 +1063,7 @@
     <t>Expeditionary District</t>
   </si>
   <si>
-    <t>P0</t>
-  </si>
-  <si>
-    <t>GRD</t>
-  </si>
-  <si>
     <t>CEGRD</t>
-  </si>
-  <si>
-    <t>Gulf Region District</t>
-  </si>
-  <si>
-    <t>US Army Engineer District, Gulf Region</t>
   </si>
   <si>
     <t>Division</t>
@@ -1647,12 +1632,30 @@
   <si>
     <t>https://services7.arcgis.com/n1YM8pTrFmm7L4hs/arcgis/rest/services/fuds/FeatureServer/9/query?outFields=*&amp;where=DIST%3D%27SPK%27&amp;f=geojson</t>
   </si>
+  <si>
+    <t>Middle East District</t>
+  </si>
+  <si>
+    <t>US Army Engineer District, Middle East</t>
+  </si>
+  <si>
+    <t>SWM</t>
+  </si>
+  <si>
+    <t>CESWM</t>
+  </si>
+  <si>
+    <t>CESWE</t>
+  </si>
+  <si>
+    <t>SWE</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1709,6 +1712,19 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1768,10 +1784,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1794,9 +1811,11 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2018,10 +2037,10 @@
   <cols>
     <col min="1" max="1" width="19.6640625" customWidth="1"/>
     <col min="2" max="2" width="32.5" customWidth="1"/>
-    <col min="8" max="8" width="78.1640625" customWidth="1"/>
+    <col min="8" max="8" width="127.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:8" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2047,7 +2066,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>8</v>
       </c>
@@ -2065,7 +2084,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>8</v>
       </c>
@@ -2085,7 +2104,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
         <v>8</v>
       </c>
@@ -2108,7 +2127,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:8" ht="57" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>8</v>
       </c>
@@ -2128,7 +2147,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:8" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
@@ -2165,7 +2184,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
@@ -2183,7 +2202,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:8" ht="29" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2201,7 +2220,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:8" ht="29" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
         <v>8</v>
       </c>
@@ -2219,7 +2238,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
         <v>8</v>
       </c>
@@ -2239,7 +2258,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
@@ -2257,7 +2276,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
         <v>8</v>
       </c>
@@ -2277,7 +2296,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
         <v>8</v>
       </c>
@@ -2297,7 +2316,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
         <v>8</v>
       </c>
@@ -2317,7 +2336,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
         <v>8</v>
       </c>
@@ -2337,7 +2356,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
         <v>44</v>
       </c>
@@ -2377,7 +2396,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
         <v>44</v>
       </c>
@@ -2439,7 +2458,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
         <v>52</v>
       </c>
@@ -2479,7 +2498,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
         <v>52</v>
       </c>
@@ -2527,7 +2546,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
         <v>56</v>
       </c>
@@ -2567,7 +2586,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
         <v>56</v>
       </c>
@@ -2615,7 +2634,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
         <v>60</v>
       </c>
@@ -2655,7 +2674,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:8" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
         <v>60</v>
       </c>
@@ -5602,8 +5621,11 @@
   <dimension ref="A1:AE999"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.5" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
+    <col min="2" max="2" width="27.6640625" customWidth="1"/>
+    <col min="5" max="5" width="28.6640625" customWidth="1"/>
     <col min="6" max="6" width="69.83203125" customWidth="1"/>
     <col min="7" max="7" width="67.5" customWidth="1"/>
+    <col min="8" max="8" width="52.5" customWidth="1"/>
     <col min="9" max="9" width="37.1640625" customWidth="1"/>
     <col min="10" max="10" width="61.33203125" customWidth="1"/>
     <col min="11" max="11" width="43.1640625" customWidth="1"/>
@@ -5612,7 +5634,7 @@
     <col min="15" max="15" width="77.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
         <v>9</v>
       </c>
@@ -5675,46 +5697,44 @@
       <c r="AD1" s="5"/>
       <c r="AE1" s="5"/>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>64</v>
+        <v>339</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>65</v>
+        <v>340</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>66</v>
+        <v>341</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>67</v>
+        <v>342</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>68</v>
+        <v>343</v>
       </c>
       <c r="G2" s="5"/>
       <c r="H2" s="5" t="s">
-        <v>69</v>
+        <v>344</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>70</v>
+        <v>343</v>
       </c>
       <c r="J2" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L2" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M2" s="5"/>
       <c r="N2" s="5"/>
-      <c r="O2" s="5" t="s">
-        <v>67</v>
-      </c>
+      <c r="O2" s="5"/>
       <c r="P2" s="5"/>
       <c r="Q2" s="5"/>
       <c r="R2" s="5"/>
@@ -5732,46 +5752,46 @@
       <c r="AD2" s="5"/>
       <c r="AE2" s="5"/>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B3" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C3" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>73</v>
-      </c>
       <c r="D3" s="5" t="s">
-        <v>74</v>
+        <v>346</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>75</v>
+        <v>347</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="G3" s="5"/>
       <c r="H3" s="5" t="s">
-        <v>77</v>
+        <v>348</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="J3" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5" t="s">
-        <v>75</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L3" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M3" s="5"/>
+      <c r="N3" s="5" t="s">
+        <v>347</v>
+      </c>
+      <c r="O3" s="5"/>
       <c r="P3" s="5"/>
       <c r="Q3" s="5"/>
       <c r="R3" s="5"/>
@@ -5789,7 +5809,7 @@
       <c r="AD3" s="5"/>
       <c r="AE3" s="5"/>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>63</v>
       </c>
@@ -5797,23 +5817,23 @@
         <v>64</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="G4" s="5"/>
       <c r="H4" s="5" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="J4" s="5" t="s">
         <v>71</v>
@@ -5827,7 +5847,7 @@
       </c>
       <c r="N4" s="5"/>
       <c r="O4" s="5" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="P4" s="5"/>
       <c r="Q4" s="5"/>
@@ -5846,7 +5866,7 @@
       <c r="AD4" s="5"/>
       <c r="AE4" s="5"/>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A5" s="5" t="s">
         <v>63</v>
       </c>
@@ -5854,23 +5874,23 @@
         <v>64</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="5" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="J5" s="5" t="s">
         <v>71</v>
@@ -5884,7 +5904,7 @@
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="P5" s="5"/>
       <c r="Q5" s="5"/>
@@ -5903,7 +5923,7 @@
       <c r="AD5" s="5"/>
       <c r="AE5" s="5"/>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A6" s="5" t="s">
         <v>63</v>
       </c>
@@ -5911,23 +5931,23 @@
         <v>64</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="G6" s="5"/>
       <c r="H6" s="5" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="I6" s="5" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="J6" s="5" t="s">
         <v>71</v>
@@ -5941,7 +5961,7 @@
       </c>
       <c r="N6" s="5"/>
       <c r="O6" s="5" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="P6" s="5"/>
       <c r="Q6" s="5"/>
@@ -5960,7 +5980,7 @@
       <c r="AD6" s="5"/>
       <c r="AE6" s="5"/>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A7" s="5" t="s">
         <v>63</v>
       </c>
@@ -5968,23 +5988,23 @@
         <v>64</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G7" s="5"/>
       <c r="H7" s="5" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="J7" s="5" t="s">
         <v>71</v>
@@ -5998,7 +6018,7 @@
       </c>
       <c r="N7" s="5"/>
       <c r="O7" s="5" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="P7" s="5"/>
       <c r="Q7" s="5"/>
@@ -6017,45 +6037,45 @@
       <c r="AD7" s="5"/>
       <c r="AE7" s="5"/>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A8" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="G8" s="5"/>
       <c r="H8" s="5" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>109</v>
+        <v>96</v>
       </c>
       <c r="J8" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="L8" s="5"/>
       <c r="M8" s="5" t="s">
-        <v>103</v>
+        <v>64</v>
       </c>
       <c r="N8" s="5"/>
       <c r="O8" s="5" t="s">
-        <v>106</v>
+        <v>93</v>
       </c>
       <c r="P8" s="5"/>
       <c r="Q8" s="5"/>
@@ -6074,45 +6094,45 @@
       <c r="AD8" s="5"/>
       <c r="AE8" s="5"/>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A9" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>112</v>
+        <v>98</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>114</v>
+        <v>100</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="5" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="J9" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="L9" s="5"/>
       <c r="M9" s="5" t="s">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="N9" s="5"/>
       <c r="O9" s="5" t="s">
-        <v>113</v>
+        <v>99</v>
       </c>
       <c r="P9" s="5"/>
       <c r="Q9" s="5"/>
@@ -6131,46 +6151,46 @@
       <c r="AD9" s="5"/>
       <c r="AE9" s="5"/>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A10" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C10" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>115</v>
-      </c>
       <c r="D10" s="5" t="s">
-        <v>116</v>
+        <v>349</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>117</v>
+        <v>350</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G10" s="5"/>
       <c r="H10" s="5" t="s">
-        <v>119</v>
+        <v>351</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="J10" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="L10" s="5"/>
-      <c r="M10" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="N10" s="5"/>
-      <c r="O10" s="5" t="s">
-        <v>117</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M10" s="5"/>
+      <c r="N10" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="O10" s="5"/>
       <c r="P10" s="5"/>
       <c r="Q10" s="5"/>
       <c r="R10" s="5"/>
@@ -6188,7 +6208,7 @@
       <c r="AD10" s="5"/>
       <c r="AE10" s="5"/>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A11" s="5" t="s">
         <v>63</v>
       </c>
@@ -6196,23 +6216,23 @@
         <v>103</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>124</v>
+        <v>107</v>
       </c>
       <c r="G11" s="5"/>
       <c r="H11" s="5" t="s">
-        <v>125</v>
+        <v>108</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="J11" s="5" t="s">
         <v>71</v>
@@ -6226,7 +6246,7 @@
       </c>
       <c r="N11" s="5"/>
       <c r="O11" s="5" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="P11" s="5"/>
       <c r="Q11" s="5"/>
@@ -6245,31 +6265,31 @@
       <c r="AD11" s="5"/>
       <c r="AE11" s="5"/>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A12" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>127</v>
+        <v>111</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>128</v>
+        <v>112</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="G12" s="5"/>
       <c r="H12" s="5" t="s">
-        <v>131</v>
+        <v>114</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>132</v>
+        <v>114</v>
       </c>
       <c r="J12" s="5" t="s">
         <v>71</v>
@@ -6279,11 +6299,11 @@
       </c>
       <c r="L12" s="5"/>
       <c r="M12" s="5" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N12" s="5"/>
       <c r="O12" s="5" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="P12" s="5"/>
       <c r="Q12" s="5"/>
@@ -6302,7 +6322,7 @@
       <c r="AD12" s="5"/>
       <c r="AE12" s="5"/>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A13" s="5" t="s">
         <v>63</v>
       </c>
@@ -6310,23 +6330,23 @@
         <v>103</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>133</v>
+        <v>115</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>134</v>
+        <v>116</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>136</v>
+        <v>118</v>
       </c>
       <c r="G13" s="5"/>
       <c r="H13" s="5" t="s">
-        <v>137</v>
+        <v>119</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
       <c r="J13" s="5" t="s">
         <v>71</v>
@@ -6340,7 +6360,7 @@
       </c>
       <c r="N13" s="5"/>
       <c r="O13" s="5" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="P13" s="5"/>
       <c r="Q13" s="5"/>
@@ -6359,7 +6379,7 @@
       <c r="AD13" s="5"/>
       <c r="AE13" s="5"/>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>63</v>
       </c>
@@ -6367,26 +6387,26 @@
         <v>103</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>140</v>
+        <v>122</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="G14" s="5"/>
       <c r="H14" s="5" t="s">
-        <v>143</v>
+        <v>125</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>144</v>
+        <v>126</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>110</v>
@@ -6397,7 +6417,7 @@
       </c>
       <c r="N14" s="5"/>
       <c r="O14" s="5" t="s">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="P14" s="5"/>
       <c r="Q14" s="5"/>
@@ -6416,45 +6436,45 @@
       <c r="AD14" s="5"/>
       <c r="AE14" s="5"/>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>147</v>
+        <v>127</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="G15" s="5"/>
       <c r="H15" s="5" t="s">
-        <v>151</v>
+        <v>131</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>152</v>
+        <v>132</v>
       </c>
       <c r="J15" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="L15" s="5"/>
       <c r="M15" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="N15" s="5"/>
       <c r="O15" s="5" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="P15" s="5"/>
       <c r="Q15" s="5"/>
@@ -6473,45 +6493,45 @@
       <c r="AD15" s="5"/>
       <c r="AE15" s="5"/>
     </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>154</v>
+        <v>133</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>155</v>
+        <v>134</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>157</v>
+        <v>136</v>
       </c>
       <c r="G16" s="5"/>
       <c r="H16" s="5" t="s">
-        <v>158</v>
+        <v>137</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>159</v>
+        <v>138</v>
       </c>
       <c r="J16" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="L16" s="5"/>
       <c r="M16" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="N16" s="5"/>
       <c r="O16" s="5" t="s">
-        <v>156</v>
+        <v>135</v>
       </c>
       <c r="P16" s="5"/>
       <c r="Q16" s="5"/>
@@ -6530,45 +6550,45 @@
       <c r="AD16" s="5"/>
       <c r="AE16" s="5"/>
     </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>160</v>
+        <v>139</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>161</v>
+        <v>140</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>163</v>
+        <v>142</v>
       </c>
       <c r="G17" s="5"/>
       <c r="H17" s="5" t="s">
-        <v>164</v>
+        <v>143</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>165</v>
+        <v>144</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>153</v>
+        <v>110</v>
       </c>
       <c r="L17" s="5"/>
       <c r="M17" s="5" t="s">
-        <v>146</v>
+        <v>103</v>
       </c>
       <c r="N17" s="5"/>
       <c r="O17" s="5" t="s">
-        <v>162</v>
+        <v>141</v>
       </c>
       <c r="P17" s="5"/>
       <c r="Q17" s="5"/>
@@ -6587,46 +6607,46 @@
       <c r="AD17" s="5"/>
       <c r="AE17" s="5"/>
     </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B18" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C18" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="5" t="s">
-        <v>166</v>
-      </c>
       <c r="D18" s="5" t="s">
-        <v>167</v>
+        <v>352</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>168</v>
+        <v>353</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="5" t="s">
-        <v>170</v>
+        <v>354</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="J18" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="L18" s="5"/>
-      <c r="M18" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="N18" s="5"/>
-      <c r="O18" s="5" t="s">
-        <v>168</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M18" s="5"/>
+      <c r="N18" s="5" t="s">
+        <v>353</v>
+      </c>
+      <c r="O18" s="5"/>
       <c r="P18" s="5"/>
       <c r="Q18" s="5"/>
       <c r="R18" s="5"/>
@@ -6644,7 +6664,7 @@
       <c r="AD18" s="5"/>
       <c r="AE18" s="5"/>
     </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="5" t="s">
         <v>63</v>
       </c>
@@ -6652,23 +6672,23 @@
         <v>146</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>172</v>
+        <v>147</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>173</v>
+        <v>148</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>175</v>
+        <v>150</v>
       </c>
       <c r="G19" s="5"/>
       <c r="H19" s="5" t="s">
-        <v>176</v>
+        <v>151</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>177</v>
+        <v>152</v>
       </c>
       <c r="J19" s="5" t="s">
         <v>71</v>
@@ -6682,7 +6702,7 @@
       </c>
       <c r="N19" s="5"/>
       <c r="O19" s="5" t="s">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="P19" s="5"/>
       <c r="Q19" s="5"/>
@@ -6701,45 +6721,45 @@
       <c r="AD19" s="5"/>
       <c r="AE19" s="5"/>
     </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>180</v>
+        <v>155</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>182</v>
+        <v>157</v>
       </c>
       <c r="G20" s="5"/>
       <c r="H20" s="5" t="s">
-        <v>183</v>
+        <v>158</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>184</v>
+        <v>159</v>
       </c>
       <c r="J20" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="L20" s="5"/>
       <c r="M20" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="N20" s="5"/>
       <c r="O20" s="5" t="s">
-        <v>181</v>
+        <v>156</v>
       </c>
       <c r="P20" s="5"/>
       <c r="Q20" s="5"/>
@@ -6758,45 +6778,45 @@
       <c r="AD20" s="5"/>
       <c r="AE20" s="5"/>
     </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>186</v>
+        <v>160</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="G21" s="5"/>
       <c r="H21" s="5" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="J21" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="L21" s="5"/>
       <c r="M21" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="N21" s="5"/>
       <c r="O21" s="5" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
       <c r="P21" s="5"/>
       <c r="Q21" s="5"/>
@@ -6815,45 +6835,45 @@
       <c r="AD21" s="5"/>
       <c r="AE21" s="5"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="5" t="s">
-        <v>196</v>
+        <v>170</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>197</v>
+        <v>171</v>
       </c>
       <c r="J22" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="L22" s="5"/>
       <c r="M22" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="N22" s="5"/>
       <c r="O22" s="5" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="P22" s="5"/>
       <c r="Q22" s="5"/>
@@ -6872,45 +6892,45 @@
       <c r="AD22" s="5"/>
       <c r="AE22" s="5"/>
     </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>198</v>
+        <v>172</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>201</v>
+        <v>175</v>
       </c>
       <c r="G23" s="5"/>
       <c r="H23" s="5" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>203</v>
+        <v>177</v>
       </c>
       <c r="J23" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>185</v>
+        <v>153</v>
       </c>
       <c r="L23" s="5"/>
       <c r="M23" s="5" t="s">
-        <v>178</v>
+        <v>146</v>
       </c>
       <c r="N23" s="5"/>
       <c r="O23" s="5" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="P23" s="5"/>
       <c r="Q23" s="5"/>
@@ -6929,46 +6949,48 @@
       <c r="AD23" s="5"/>
       <c r="AE23" s="5"/>
     </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B24" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C24" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="C24" s="5" t="s">
-        <v>204</v>
-      </c>
       <c r="D24" s="5" t="s">
-        <v>205</v>
+        <v>355</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>206</v>
+        <v>356</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>207</v>
-      </c>
-      <c r="G24" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="G24" s="5" t="s">
+        <v>357</v>
+      </c>
       <c r="H24" s="5" t="s">
-        <v>208</v>
+        <v>358</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>209</v>
+        <v>185</v>
       </c>
       <c r="J24" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="L24" s="5"/>
-      <c r="M24" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="N24" s="5"/>
-      <c r="O24" s="5" t="s">
-        <v>206</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M24" s="5"/>
+      <c r="N24" s="5" t="s">
+        <v>359</v>
+      </c>
+      <c r="O24" s="5"/>
       <c r="P24" s="5"/>
       <c r="Q24" s="5"/>
       <c r="R24" s="5"/>
@@ -6986,7 +7008,7 @@
       <c r="AD24" s="5"/>
       <c r="AE24" s="5"/>
     </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="5" t="s">
         <v>63</v>
       </c>
@@ -6994,23 +7016,23 @@
         <v>178</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="G25" s="5"/>
       <c r="H25" s="5" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="J25" s="5" t="s">
         <v>71</v>
@@ -7024,7 +7046,7 @@
       </c>
       <c r="N25" s="5"/>
       <c r="O25" s="5" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="P25" s="5"/>
       <c r="Q25" s="5"/>
@@ -7043,7 +7065,7 @@
       <c r="AD25" s="5"/>
       <c r="AE25" s="5"/>
     </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="5" t="s">
         <v>63</v>
       </c>
@@ -7051,23 +7073,23 @@
         <v>178</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>216</v>
+        <v>186</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>217</v>
+        <v>187</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>219</v>
+        <v>189</v>
       </c>
       <c r="G26" s="5"/>
       <c r="H26" s="5" t="s">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>221</v>
+        <v>191</v>
       </c>
       <c r="J26" s="5" t="s">
         <v>71</v>
@@ -7081,7 +7103,7 @@
       </c>
       <c r="N26" s="5"/>
       <c r="O26" s="5" t="s">
-        <v>218</v>
+        <v>188</v>
       </c>
       <c r="P26" s="5"/>
       <c r="Q26" s="5"/>
@@ -7100,45 +7122,45 @@
       <c r="AD26" s="5"/>
       <c r="AE26" s="5"/>
     </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="G27" s="5"/>
       <c r="H27" s="5" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="I27" s="5" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="J27" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="L27" s="5"/>
       <c r="M27" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="N27" s="5"/>
       <c r="O27" s="5" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="P27" s="5"/>
       <c r="Q27" s="5"/>
@@ -7157,45 +7179,45 @@
       <c r="AD27" s="5"/>
       <c r="AE27" s="5"/>
     </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A28" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>231</v>
+        <v>199</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>233</v>
+        <v>201</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5" t="s">
-        <v>234</v>
+        <v>202</v>
       </c>
       <c r="I28" s="5" t="s">
-        <v>235</v>
+        <v>203</v>
       </c>
       <c r="J28" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="N28" s="5"/>
       <c r="O28" s="5" t="s">
-        <v>232</v>
+        <v>200</v>
       </c>
       <c r="P28" s="5"/>
       <c r="Q28" s="5"/>
@@ -7214,45 +7236,45 @@
       <c r="AD28" s="5"/>
       <c r="AE28" s="5"/>
     </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>236</v>
+        <v>204</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>237</v>
+        <v>205</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>239</v>
+        <v>207</v>
       </c>
       <c r="G29" s="5"/>
       <c r="H29" s="5" t="s">
-        <v>240</v>
+        <v>208</v>
       </c>
       <c r="I29" s="5" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="J29" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K29" s="5" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="L29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5" t="s">
-        <v>238</v>
+        <v>206</v>
       </c>
       <c r="P29" s="5"/>
       <c r="Q29" s="5"/>
@@ -7271,45 +7293,45 @@
       <c r="AD29" s="5"/>
       <c r="AE29" s="5"/>
     </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A30" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>243</v>
+        <v>211</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>245</v>
+        <v>213</v>
       </c>
       <c r="G30" s="5"/>
       <c r="H30" s="5" t="s">
-        <v>246</v>
+        <v>214</v>
       </c>
       <c r="I30" s="5" t="s">
-        <v>247</v>
+        <v>215</v>
       </c>
       <c r="J30" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K30" s="5" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="L30" s="5"/>
       <c r="M30" s="5" t="s">
-        <v>222</v>
+        <v>178</v>
       </c>
       <c r="N30" s="5"/>
       <c r="O30" s="5" t="s">
-        <v>244</v>
+        <v>212</v>
       </c>
       <c r="P30" s="5"/>
       <c r="Q30" s="5"/>
@@ -7328,45 +7350,45 @@
       <c r="AD30" s="5"/>
       <c r="AE30" s="5"/>
     </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A31" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>249</v>
+        <v>216</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>252</v>
+        <v>219</v>
       </c>
       <c r="G31" s="5"/>
       <c r="H31" s="5" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="I31" s="5" t="s">
-        <v>254</v>
+        <v>221</v>
       </c>
       <c r="J31" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K31" s="5" t="s">
-        <v>255</v>
+        <v>185</v>
       </c>
       <c r="L31" s="5"/>
       <c r="M31" s="5" t="s">
-        <v>248</v>
+        <v>178</v>
       </c>
       <c r="N31" s="5"/>
       <c r="O31" s="5" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="P31" s="5"/>
       <c r="Q31" s="5"/>
@@ -7385,46 +7407,46 @@
       <c r="AD31" s="5"/>
       <c r="AE31" s="5"/>
     </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A32" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>248</v>
+        <v>339</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>256</v>
+        <v>222</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>257</v>
+        <v>360</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>258</v>
+        <v>361</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>259</v>
+        <v>229</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="5" t="s">
-        <v>260</v>
+        <v>362</v>
       </c>
       <c r="I32" s="5" t="s">
-        <v>261</v>
+        <v>229</v>
       </c>
       <c r="J32" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K32" s="5" t="s">
-        <v>255</v>
-      </c>
-      <c r="L32" s="5"/>
-      <c r="M32" s="5" t="s">
-        <v>248</v>
-      </c>
-      <c r="N32" s="5"/>
-      <c r="O32" s="5" t="s">
-        <v>258</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L32" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M32" s="5"/>
+      <c r="N32" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="O32" s="5"/>
       <c r="P32" s="5"/>
       <c r="Q32" s="5"/>
       <c r="R32" s="5"/>
@@ -7442,45 +7464,45 @@
       <c r="AD32" s="5"/>
       <c r="AE32" s="5"/>
     </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A33" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>263</v>
+        <v>224</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>265</v>
+        <v>226</v>
       </c>
       <c r="G33" s="5"/>
       <c r="H33" s="5" t="s">
-        <v>266</v>
+        <v>227</v>
       </c>
       <c r="I33" s="5" t="s">
-        <v>267</v>
+        <v>228</v>
       </c>
       <c r="J33" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K33" s="5" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="L33" s="5"/>
       <c r="M33" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="N33" s="5"/>
       <c r="O33" s="5" t="s">
-        <v>264</v>
+        <v>225</v>
       </c>
       <c r="P33" s="5"/>
       <c r="Q33" s="5"/>
@@ -7499,45 +7521,45 @@
       <c r="AD33" s="5"/>
       <c r="AE33" s="5"/>
     </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A34" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C34" s="5" t="s">
-        <v>268</v>
+        <v>230</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>269</v>
+        <v>231</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>271</v>
+        <v>233</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="5" t="s">
-        <v>272</v>
+        <v>234</v>
       </c>
       <c r="I34" s="5" t="s">
-        <v>273</v>
+        <v>235</v>
       </c>
       <c r="J34" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K34" s="5" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="L34" s="5"/>
       <c r="M34" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="N34" s="5"/>
       <c r="O34" s="5" t="s">
-        <v>270</v>
+        <v>232</v>
       </c>
       <c r="P34" s="5"/>
       <c r="Q34" s="5"/>
@@ -7556,45 +7578,45 @@
       <c r="AD34" s="5"/>
       <c r="AE34" s="5"/>
     </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A35" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>274</v>
+        <v>236</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>275</v>
+        <v>237</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>277</v>
+        <v>239</v>
       </c>
       <c r="G35" s="5"/>
       <c r="H35" s="5" t="s">
-        <v>278</v>
+        <v>240</v>
       </c>
       <c r="I35" s="5" t="s">
-        <v>279</v>
+        <v>241</v>
       </c>
       <c r="J35" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K35" s="5" t="s">
-        <v>255</v>
+        <v>229</v>
       </c>
       <c r="L35" s="5"/>
       <c r="M35" s="5" t="s">
-        <v>248</v>
+        <v>222</v>
       </c>
       <c r="N35" s="5"/>
       <c r="O35" s="5" t="s">
-        <v>276</v>
+        <v>238</v>
       </c>
       <c r="P35" s="5"/>
       <c r="Q35" s="5"/>
@@ -7613,45 +7635,45 @@
       <c r="AD35" s="5"/>
       <c r="AE35" s="5"/>
     </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A36" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>281</v>
+        <v>242</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>282</v>
+        <v>243</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>284</v>
+        <v>245</v>
       </c>
       <c r="G36" s="5"/>
       <c r="H36" s="5" t="s">
-        <v>285</v>
+        <v>246</v>
       </c>
       <c r="I36" s="5" t="s">
-        <v>286</v>
+        <v>247</v>
       </c>
       <c r="J36" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K36" s="5" t="s">
-        <v>287</v>
+        <v>229</v>
       </c>
       <c r="L36" s="5"/>
       <c r="M36" s="5" t="s">
-        <v>280</v>
+        <v>222</v>
       </c>
       <c r="N36" s="5"/>
       <c r="O36" s="5" t="s">
-        <v>283</v>
+        <v>244</v>
       </c>
       <c r="P36" s="5"/>
       <c r="Q36" s="5"/>
@@ -7670,46 +7692,46 @@
       <c r="AD36" s="5"/>
       <c r="AE36" s="5"/>
     </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A37" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>280</v>
+        <v>339</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>288</v>
+        <v>248</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>289</v>
+        <v>363</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>290</v>
+        <v>364</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>291</v>
+        <v>255</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="5" t="s">
-        <v>292</v>
+        <v>365</v>
       </c>
       <c r="I37" s="5" t="s">
-        <v>293</v>
+        <v>255</v>
       </c>
       <c r="J37" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K37" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="N37" s="5"/>
-      <c r="O37" s="5" t="s">
-        <v>290</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L37" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M37" s="5"/>
+      <c r="N37" s="5" t="s">
+        <v>364</v>
+      </c>
+      <c r="O37" s="5"/>
       <c r="P37" s="5"/>
       <c r="Q37" s="5"/>
       <c r="R37" s="5"/>
@@ -7727,45 +7749,45 @@
       <c r="AD37" s="5"/>
       <c r="AE37" s="5"/>
     </row>
-    <row r="38" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A38" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>294</v>
+        <v>249</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>295</v>
+        <v>250</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>297</v>
+        <v>252</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="5" t="s">
-        <v>298</v>
+        <v>253</v>
       </c>
       <c r="I38" s="5" t="s">
-        <v>299</v>
+        <v>254</v>
       </c>
       <c r="J38" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K38" s="5" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="L38" s="5"/>
       <c r="M38" s="5" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="N38" s="5"/>
       <c r="O38" s="5" t="s">
-        <v>296</v>
+        <v>251</v>
       </c>
       <c r="P38" s="5"/>
       <c r="Q38" s="5"/>
@@ -7784,45 +7806,45 @@
       <c r="AD38" s="5"/>
       <c r="AE38" s="5"/>
     </row>
-    <row r="39" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A39" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>300</v>
+        <v>256</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>301</v>
+        <v>257</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>303</v>
+        <v>259</v>
       </c>
       <c r="G39" s="5"/>
       <c r="H39" s="5" t="s">
-        <v>304</v>
+        <v>260</v>
       </c>
       <c r="I39" s="5" t="s">
-        <v>305</v>
+        <v>261</v>
       </c>
       <c r="J39" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K39" s="5" t="s">
-        <v>287</v>
+        <v>255</v>
       </c>
       <c r="L39" s="5"/>
       <c r="M39" s="5" t="s">
-        <v>280</v>
+        <v>248</v>
       </c>
       <c r="N39" s="5"/>
       <c r="O39" s="5" t="s">
-        <v>302</v>
+        <v>258</v>
       </c>
       <c r="P39" s="5"/>
       <c r="Q39" s="5"/>
@@ -7841,45 +7863,45 @@
       <c r="AD39" s="5"/>
       <c r="AE39" s="5"/>
     </row>
-    <row r="40" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A40" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>307</v>
+        <v>262</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>308</v>
+        <v>263</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>310</v>
+        <v>265</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="5" t="s">
-        <v>311</v>
+        <v>266</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>312</v>
+        <v>267</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K40" s="5" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="L40" s="5"/>
       <c r="M40" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="N40" s="5"/>
       <c r="O40" s="5" t="s">
-        <v>309</v>
+        <v>264</v>
       </c>
       <c r="P40" s="5"/>
       <c r="Q40" s="5"/>
@@ -7898,45 +7920,45 @@
       <c r="AD40" s="5"/>
       <c r="AE40" s="5"/>
     </row>
-    <row r="41" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A41" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>314</v>
+        <v>268</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>315</v>
+        <v>269</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>317</v>
+        <v>271</v>
       </c>
       <c r="G41" s="5"/>
       <c r="H41" s="5" t="s">
-        <v>318</v>
+        <v>272</v>
       </c>
       <c r="I41" s="5" t="s">
-        <v>319</v>
+        <v>273</v>
       </c>
       <c r="J41" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K41" s="5" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="L41" s="5"/>
       <c r="M41" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="N41" s="5"/>
       <c r="O41" s="5" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
       <c r="P41" s="5"/>
       <c r="Q41" s="5"/>
@@ -7955,45 +7977,45 @@
       <c r="AD41" s="5"/>
       <c r="AE41" s="5"/>
     </row>
-    <row r="42" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A42" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="C42" s="5" t="s">
-        <v>320</v>
+        <v>274</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>321</v>
+        <v>275</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>323</v>
+        <v>277</v>
       </c>
       <c r="G42" s="5"/>
       <c r="H42" s="5" t="s">
-        <v>324</v>
+        <v>278</v>
       </c>
       <c r="I42" s="5" t="s">
-        <v>325</v>
+        <v>279</v>
       </c>
       <c r="J42" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K42" s="5" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="L42" s="5"/>
       <c r="M42" s="5" t="s">
-        <v>306</v>
+        <v>248</v>
       </c>
       <c r="N42" s="5"/>
       <c r="O42" s="5" t="s">
-        <v>322</v>
+        <v>276</v>
       </c>
       <c r="P42" s="5"/>
       <c r="Q42" s="5"/>
@@ -8012,46 +8034,46 @@
       <c r="AD42" s="5"/>
       <c r="AE42" s="5"/>
     </row>
-    <row r="43" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A43" s="5" t="s">
-        <v>63</v>
+        <v>338</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>306</v>
+        <v>339</v>
       </c>
       <c r="C43" s="5" t="s">
-        <v>326</v>
+        <v>280</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>327</v>
+        <v>366</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>328</v>
+        <v>367</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>329</v>
+        <v>287</v>
       </c>
       <c r="G43" s="5"/>
       <c r="H43" s="5" t="s">
-        <v>330</v>
+        <v>368</v>
       </c>
       <c r="I43" s="5" t="s">
-        <v>331</v>
+        <v>287</v>
       </c>
       <c r="J43" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K43" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="L43" s="5"/>
-      <c r="M43" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="N43" s="5"/>
-      <c r="O43" s="5" t="s">
-        <v>328</v>
-      </c>
+        <v>345</v>
+      </c>
+      <c r="L43" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="M43" s="5"/>
+      <c r="N43" s="5" t="s">
+        <v>367</v>
+      </c>
+      <c r="O43" s="5"/>
       <c r="P43" s="5"/>
       <c r="Q43" s="5"/>
       <c r="R43" s="5"/>
@@ -8069,47 +8091,45 @@
       <c r="AD43" s="5"/>
       <c r="AE43" s="5"/>
     </row>
-    <row r="44" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A44" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>333</v>
+        <v>281</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>334</v>
+        <v>282</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="G44" s="5" t="s">
-        <v>337</v>
-      </c>
+        <v>284</v>
+      </c>
+      <c r="G44" s="5"/>
       <c r="H44" s="5" t="s">
-        <v>336</v>
+        <v>285</v>
       </c>
       <c r="I44" s="5" t="s">
-        <v>336</v>
+        <v>286</v>
       </c>
       <c r="J44" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K44" s="5" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="L44" s="5"/>
       <c r="M44" s="5" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="N44" s="5"/>
       <c r="O44" s="5" t="s">
-        <v>335</v>
+        <v>283</v>
       </c>
       <c r="P44" s="5"/>
       <c r="Q44" s="5"/>
@@ -8128,45 +8148,45 @@
       <c r="AD44" s="5"/>
       <c r="AE44" s="5"/>
     </row>
-    <row r="45" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A45" s="5" t="s">
         <v>63</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>332</v>
+        <v>280</v>
       </c>
       <c r="C45" s="5" t="s">
-        <v>338</v>
+        <v>288</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>339</v>
+        <v>289</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>341</v>
+        <v>291</v>
       </c>
       <c r="G45" s="5"/>
       <c r="H45" s="5" t="s">
-        <v>341</v>
+        <v>292</v>
       </c>
       <c r="I45" s="5" t="s">
-        <v>342</v>
+        <v>293</v>
       </c>
       <c r="J45" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K45" s="5" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="L45" s="5"/>
       <c r="M45" s="5" t="s">
-        <v>306</v>
+        <v>280</v>
       </c>
       <c r="N45" s="5"/>
       <c r="O45" s="5" t="s">
-        <v>340</v>
+        <v>290</v>
       </c>
       <c r="P45" s="5"/>
       <c r="Q45" s="5"/>
@@ -8185,44 +8205,46 @@
       <c r="AD45" s="5"/>
       <c r="AE45" s="5"/>
     </row>
-    <row r="46" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A46" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="C46" s="5" t="s">
-        <v>345</v>
+        <v>294</v>
       </c>
       <c r="D46" s="5" t="s">
-        <v>346</v>
+        <v>295</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>347</v>
+        <v>296</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>348</v>
+        <v>297</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="5" t="s">
-        <v>349</v>
+        <v>298</v>
       </c>
       <c r="I46" s="5" t="s">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="J46" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L46" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M46" s="5"/>
+        <v>287</v>
+      </c>
+      <c r="L46" s="5"/>
+      <c r="M46" s="5" t="s">
+        <v>280</v>
+      </c>
       <c r="N46" s="5"/>
-      <c r="O46" s="5"/>
+      <c r="O46" s="5" t="s">
+        <v>296</v>
+      </c>
       <c r="P46" s="5"/>
       <c r="Q46" s="5"/>
       <c r="R46" s="5"/>
@@ -8240,46 +8262,46 @@
       <c r="AD46" s="5"/>
       <c r="AE46" s="5"/>
     </row>
-    <row r="47" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A47" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>344</v>
+        <v>280</v>
       </c>
       <c r="C47" s="5" t="s">
-        <v>64</v>
+        <v>300</v>
       </c>
       <c r="D47" s="5" t="s">
-        <v>351</v>
+        <v>301</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>352</v>
+        <v>302</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>72</v>
+        <v>303</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="5" t="s">
-        <v>353</v>
+        <v>304</v>
       </c>
       <c r="I47" s="5" t="s">
-        <v>72</v>
+        <v>305</v>
       </c>
       <c r="J47" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K47" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L47" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M47" s="5"/>
-      <c r="N47" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="O47" s="5"/>
+        <v>287</v>
+      </c>
+      <c r="L47" s="5"/>
+      <c r="M47" s="5" t="s">
+        <v>280</v>
+      </c>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5" t="s">
+        <v>302</v>
+      </c>
       <c r="P47" s="5"/>
       <c r="Q47" s="5"/>
       <c r="R47" s="5"/>
@@ -8297,44 +8319,44 @@
       <c r="AD47" s="5"/>
       <c r="AE47" s="5"/>
     </row>
-    <row r="48" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A48" s="5" t="s">
-        <v>343</v>
+        <v>338</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C48" s="5" t="s">
-        <v>103</v>
+        <v>306</v>
       </c>
       <c r="D48" s="5" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>110</v>
+        <v>313</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="5" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="I48" s="5" t="s">
-        <v>110</v>
+        <v>313</v>
       </c>
       <c r="J48" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K48" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L48" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M48" s="5"/>
       <c r="N48" s="5" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="O48" s="5"/>
       <c r="P48" s="5"/>
@@ -8354,46 +8376,46 @@
       <c r="AD48" s="5"/>
       <c r="AE48" s="5"/>
     </row>
-    <row r="49" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A49" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="C49" s="5" t="s">
-        <v>146</v>
+        <v>307</v>
       </c>
       <c r="D49" s="5" t="s">
-        <v>357</v>
+        <v>308</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>358</v>
+        <v>309</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>153</v>
+        <v>310</v>
       </c>
       <c r="G49" s="5"/>
       <c r="H49" s="5" t="s">
-        <v>359</v>
+        <v>311</v>
       </c>
       <c r="I49" s="5" t="s">
-        <v>153</v>
+        <v>312</v>
       </c>
       <c r="J49" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K49" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L49" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M49" s="5"/>
-      <c r="N49" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="O49" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="L49" s="5"/>
+      <c r="M49" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N49" s="5"/>
+      <c r="O49" s="5" t="s">
+        <v>309</v>
+      </c>
       <c r="P49" s="5"/>
       <c r="Q49" s="5"/>
       <c r="R49" s="5"/>
@@ -8411,48 +8433,46 @@
       <c r="AD49" s="5"/>
       <c r="AE49" s="5"/>
     </row>
-    <row r="50" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A50" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="C50" s="5" t="s">
-        <v>178</v>
+        <v>314</v>
       </c>
       <c r="D50" s="5" t="s">
-        <v>360</v>
+        <v>315</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>361</v>
+        <v>316</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G50" s="5" t="s">
-        <v>362</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="G50" s="5"/>
       <c r="H50" s="5" t="s">
-        <v>363</v>
+        <v>318</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>185</v>
+        <v>319</v>
       </c>
       <c r="J50" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K50" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L50" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M50" s="5"/>
-      <c r="N50" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="O50" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="L50" s="5"/>
+      <c r="M50" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N50" s="5"/>
+      <c r="O50" s="5" t="s">
+        <v>316</v>
+      </c>
       <c r="P50" s="5"/>
       <c r="Q50" s="5"/>
       <c r="R50" s="5"/>
@@ -8470,46 +8490,46 @@
       <c r="AD50" s="5"/>
       <c r="AE50" s="5"/>
     </row>
-    <row r="51" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A51" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="C51" s="5" t="s">
-        <v>222</v>
+        <v>320</v>
       </c>
       <c r="D51" s="5" t="s">
-        <v>365</v>
+        <v>321</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>229</v>
+        <v>323</v>
       </c>
       <c r="G51" s="5"/>
       <c r="H51" s="5" t="s">
-        <v>367</v>
+        <v>324</v>
       </c>
       <c r="I51" s="5" t="s">
-        <v>229</v>
+        <v>325</v>
       </c>
       <c r="J51" s="5" t="s">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="K51" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L51" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M51" s="5"/>
-      <c r="N51" s="5" t="s">
-        <v>366</v>
-      </c>
-      <c r="O51" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="L51" s="5"/>
+      <c r="M51" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N51" s="5"/>
+      <c r="O51" s="5" t="s">
+        <v>322</v>
+      </c>
       <c r="P51" s="5"/>
       <c r="Q51" s="5"/>
       <c r="R51" s="5"/>
@@ -8527,46 +8547,46 @@
       <c r="AD51" s="5"/>
       <c r="AE51" s="5"/>
     </row>
-    <row r="52" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A52" s="5" t="s">
-        <v>343</v>
+        <v>63</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>344</v>
+        <v>306</v>
       </c>
       <c r="C52" s="5" t="s">
-        <v>248</v>
+        <v>326</v>
       </c>
       <c r="D52" s="5" t="s">
-        <v>368</v>
+        <v>327</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>369</v>
+        <v>328</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>255</v>
+        <v>329</v>
       </c>
       <c r="G52" s="5"/>
       <c r="H52" s="5" t="s">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="I52" s="5" t="s">
-        <v>255</v>
+        <v>331</v>
       </c>
       <c r="J52" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K52" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L52" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M52" s="5"/>
-      <c r="N52" s="5" t="s">
-        <v>369</v>
-      </c>
-      <c r="O52" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="L52" s="5"/>
+      <c r="M52" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N52" s="5"/>
+      <c r="O52" s="5" t="s">
+        <v>328</v>
+      </c>
       <c r="P52" s="5"/>
       <c r="Q52" s="5"/>
       <c r="R52" s="5"/>
@@ -8584,46 +8604,48 @@
       <c r="AD52" s="5"/>
       <c r="AE52" s="5"/>
     </row>
-    <row r="53" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A53" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>344</v>
+        <v>63</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>306</v>
       </c>
       <c r="C53" s="5" t="s">
-        <v>280</v>
-      </c>
-      <c r="D53" s="5" t="s">
-        <v>371</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>372</v>
+        <v>333</v>
+      </c>
+      <c r="D53" s="17" t="s">
+        <v>532</v>
+      </c>
+      <c r="E53" s="17" t="s">
+        <v>531</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="G53" s="5"/>
+        <v>335</v>
+      </c>
+      <c r="G53" s="5" t="s">
+        <v>336</v>
+      </c>
       <c r="H53" s="5" t="s">
-        <v>373</v>
+        <v>335</v>
       </c>
       <c r="I53" s="5" t="s">
-        <v>287</v>
+        <v>335</v>
       </c>
       <c r="J53" s="5" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L53" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M53" s="5"/>
-      <c r="N53" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="O53" s="5"/>
+        <v>313</v>
+      </c>
+      <c r="L53" s="5"/>
+      <c r="M53" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N53" s="5"/>
+      <c r="O53" s="5" t="s">
+        <v>334</v>
+      </c>
       <c r="P53" s="5"/>
       <c r="Q53" s="5"/>
       <c r="R53" s="5"/>
@@ -8641,46 +8663,46 @@
       <c r="AD53" s="5"/>
       <c r="AE53" s="5"/>
     </row>
-    <row r="54" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A54" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="C54" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B54" s="17" t="s">
         <v>306</v>
       </c>
-      <c r="D54" s="5" t="s">
-        <v>374</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="F54" s="5" t="s">
+      <c r="C54" s="17" t="s">
+        <v>332</v>
+      </c>
+      <c r="D54" s="17" t="s">
+        <v>529</v>
+      </c>
+      <c r="E54" s="17" t="s">
+        <v>530</v>
+      </c>
+      <c r="F54" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="G54" s="5"/>
+      <c r="H54" s="17" t="s">
+        <v>527</v>
+      </c>
+      <c r="I54" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="J54" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="K54" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5" t="s">
-        <v>376</v>
-      </c>
-      <c r="I54" s="5" t="s">
-        <v>313</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="K54" s="5" t="s">
-        <v>350</v>
-      </c>
-      <c r="L54" s="5" t="s">
-        <v>344</v>
-      </c>
-      <c r="M54" s="5"/>
-      <c r="N54" s="5" t="s">
-        <v>375</v>
-      </c>
-      <c r="O54" s="5"/>
+      <c r="L54" s="5"/>
+      <c r="M54" s="5" t="s">
+        <v>306</v>
+      </c>
+      <c r="N54" s="5"/>
+      <c r="O54" s="5" t="s">
+        <v>337</v>
+      </c>
       <c r="P54" s="5"/>
       <c r="Q54" s="5"/>
       <c r="R54" s="5"/>
@@ -8698,15 +8720,15 @@
       <c r="AD54" s="5"/>
       <c r="AE54" s="5"/>
     </row>
-    <row r="55" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A55" s="5" t="s">
         <v>377</v>
       </c>
       <c r="B55" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C55" s="5" t="s">
         <v>378</v>
-      </c>
-      <c r="C55" s="5" t="s">
-        <v>344</v>
       </c>
       <c r="D55" s="5" t="s">
         <v>379</v>
@@ -8715,21 +8737,23 @@
         <v>380</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="5" t="s">
-        <v>350</v>
+        <v>381</v>
       </c>
       <c r="I55" s="5" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="J55" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="K55" s="5"/>
+      <c r="K55" s="5" t="s">
+        <v>345</v>
+      </c>
       <c r="L55" s="5" t="s">
-        <v>378</v>
+        <v>339</v>
       </c>
       <c r="M55" s="5"/>
       <c r="N55" s="5"/>
@@ -8751,12 +8775,12 @@
       <c r="AD55" s="5"/>
       <c r="AE55" s="5"/>
     </row>
-    <row r="56" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A56" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C56" s="5" t="s">
         <v>383</v>
@@ -8781,10 +8805,10 @@
         <v>71</v>
       </c>
       <c r="K56" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L56" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M56" s="5"/>
       <c r="N56" s="5"/>
@@ -8806,40 +8830,38 @@
       <c r="AD56" s="5"/>
       <c r="AE56" s="5"/>
     </row>
-    <row r="57" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A57" s="5" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="C57" s="5" t="s">
-        <v>388</v>
+        <v>339</v>
       </c>
       <c r="D57" s="5" t="s">
-        <v>389</v>
+        <v>374</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>390</v>
+        <v>375</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="G57" s="5"/>
       <c r="H57" s="5" t="s">
-        <v>391</v>
+        <v>345</v>
       </c>
       <c r="I57" s="5" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
       <c r="J57" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="K57" s="5" t="s">
-        <v>350</v>
-      </c>
+      <c r="K57" s="5"/>
       <c r="L57" s="5" t="s">
-        <v>344</v>
+        <v>373</v>
       </c>
       <c r="M57" s="5"/>
       <c r="N57" s="5"/>
@@ -8861,40 +8883,40 @@
       <c r="AD57" s="5"/>
       <c r="AE57" s="5"/>
     </row>
-    <row r="58" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A58" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C58" s="5" t="s">
-        <v>393</v>
+        <v>388</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>395</v>
+        <v>390</v>
       </c>
       <c r="F58" s="8" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="G58" s="5"/>
       <c r="H58" s="5" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="I58" s="5" t="s">
-        <v>396</v>
+        <v>391</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K58" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L58" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M58" s="5"/>
       <c r="N58" s="5"/>
@@ -8916,40 +8938,40 @@
       <c r="AD58" s="5"/>
       <c r="AE58" s="5"/>
     </row>
-    <row r="59" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A59" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C59" s="5" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="5" t="s">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="I59" s="5" t="s">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L59" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M59" s="5"/>
       <c r="N59" s="5"/>
@@ -8971,40 +8993,40 @@
       <c r="AD59" s="5"/>
       <c r="AE59" s="5"/>
     </row>
-    <row r="60" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A60" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C60" s="5" t="s">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="G60" s="5"/>
       <c r="H60" s="5" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="I60" s="5" t="s">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="J60" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K60" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L60" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M60" s="5"/>
       <c r="N60" s="5"/>
@@ -9026,40 +9048,40 @@
       <c r="AD60" s="5"/>
       <c r="AE60" s="5"/>
     </row>
-    <row r="61" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A61" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C61" s="5" t="s">
-        <v>406</v>
+        <v>401</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>407</v>
+        <v>402</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>408</v>
+        <v>403</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="5" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="I61" s="5" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="J61" s="5" t="s">
         <v>71</v>
       </c>
       <c r="K61" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L61" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M61" s="5"/>
       <c r="N61" s="5"/>
@@ -9081,40 +9103,40 @@
       <c r="AD61" s="5"/>
       <c r="AE61" s="5"/>
     </row>
-    <row r="62" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A62" s="5" t="s">
-        <v>382</v>
+        <v>377</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="C62" s="5" t="s">
-        <v>410</v>
+        <v>405</v>
       </c>
       <c r="D62" s="5" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>412</v>
+        <v>407</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="5" t="s">
-        <v>413</v>
+        <v>408</v>
       </c>
       <c r="I62" s="5" t="s">
-        <v>414</v>
+        <v>409</v>
       </c>
       <c r="J62" s="5" t="s">
         <v>145</v>
       </c>
       <c r="K62" s="5" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="L62" s="5" t="s">
-        <v>344</v>
+        <v>339</v>
       </c>
       <c r="M62" s="5"/>
       <c r="N62" s="5"/>
@@ -9136,7 +9158,7 @@
       <c r="AD62" s="5"/>
       <c r="AE62" s="5"/>
     </row>
-    <row r="63" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
@@ -9169,7 +9191,7 @@
       <c r="AD63" s="5"/>
       <c r="AE63" s="5"/>
     </row>
-    <row r="64" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A64" s="5"/>
       <c r="B64" s="5"/>
       <c r="C64" s="5"/>
@@ -9202,7 +9224,7 @@
       <c r="AD64" s="5"/>
       <c r="AE64" s="5"/>
     </row>
-    <row r="65" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A65" s="5"/>
       <c r="B65" s="5"/>
       <c r="C65" s="5"/>
@@ -9235,7 +9257,7 @@
       <c r="AD65" s="5"/>
       <c r="AE65" s="5"/>
     </row>
-    <row r="66" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A66" s="5"/>
       <c r="B66" s="5"/>
       <c r="C66" s="5"/>
@@ -9268,7 +9290,7 @@
       <c r="AD66" s="5"/>
       <c r="AE66" s="5"/>
     </row>
-    <row r="67" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A67" s="5"/>
       <c r="B67" s="5"/>
       <c r="C67" s="5"/>
@@ -9301,7 +9323,7 @@
       <c r="AD67" s="5"/>
       <c r="AE67" s="5"/>
     </row>
-    <row r="68" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A68" s="5"/>
       <c r="B68" s="5"/>
       <c r="C68" s="5"/>
@@ -9334,7 +9356,7 @@
       <c r="AD68" s="5"/>
       <c r="AE68" s="5"/>
     </row>
-    <row r="69" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A69" s="5"/>
       <c r="B69" s="5"/>
       <c r="C69" s="5"/>
@@ -9367,7 +9389,7 @@
       <c r="AD69" s="5"/>
       <c r="AE69" s="5"/>
     </row>
-    <row r="70" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A70" s="5"/>
       <c r="B70" s="5"/>
       <c r="C70" s="5"/>
@@ -9400,7 +9422,7 @@
       <c r="AD70" s="5"/>
       <c r="AE70" s="5"/>
     </row>
-    <row r="71" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A71" s="5"/>
       <c r="B71" s="5"/>
       <c r="C71" s="5"/>
@@ -9433,7 +9455,7 @@
       <c r="AD71" s="5"/>
       <c r="AE71" s="5"/>
     </row>
-    <row r="72" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A72" s="5"/>
       <c r="B72" s="5"/>
       <c r="C72" s="5"/>
@@ -9466,7 +9488,7 @@
       <c r="AD72" s="5"/>
       <c r="AE72" s="5"/>
     </row>
-    <row r="73" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A73" s="5"/>
       <c r="B73" s="5"/>
       <c r="C73" s="5"/>
@@ -9499,7 +9521,7 @@
       <c r="AD73" s="5"/>
       <c r="AE73" s="5"/>
     </row>
-    <row r="74" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A74" s="5"/>
       <c r="B74" s="5"/>
       <c r="C74" s="5"/>
@@ -9532,7 +9554,7 @@
       <c r="AD74" s="5"/>
       <c r="AE74" s="5"/>
     </row>
-    <row r="75" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A75" s="5"/>
       <c r="B75" s="5"/>
       <c r="C75" s="5"/>
@@ -9565,7 +9587,7 @@
       <c r="AD75" s="5"/>
       <c r="AE75" s="5"/>
     </row>
-    <row r="76" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A76" s="5"/>
       <c r="B76" s="5"/>
       <c r="C76" s="5"/>
@@ -9598,7 +9620,7 @@
       <c r="AD76" s="5"/>
       <c r="AE76" s="5"/>
     </row>
-    <row r="77" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A77" s="5"/>
       <c r="B77" s="5"/>
       <c r="C77" s="5"/>
@@ -9631,7 +9653,7 @@
       <c r="AD77" s="5"/>
       <c r="AE77" s="5"/>
     </row>
-    <row r="78" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A78" s="5"/>
       <c r="B78" s="5"/>
       <c r="C78" s="5"/>
@@ -9664,7 +9686,7 @@
       <c r="AD78" s="5"/>
       <c r="AE78" s="5"/>
     </row>
-    <row r="79" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A79" s="5"/>
       <c r="B79" s="5"/>
       <c r="C79" s="5"/>
@@ -9697,7 +9719,7 @@
       <c r="AD79" s="5"/>
       <c r="AE79" s="5"/>
     </row>
-    <row r="80" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A80" s="5"/>
       <c r="B80" s="5"/>
       <c r="C80" s="5"/>
@@ -9730,7 +9752,7 @@
       <c r="AD80" s="5"/>
       <c r="AE80" s="5"/>
     </row>
-    <row r="81" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A81" s="5"/>
       <c r="B81" s="5"/>
       <c r="C81" s="5"/>
@@ -9763,7 +9785,7 @@
       <c r="AD81" s="5"/>
       <c r="AE81" s="5"/>
     </row>
-    <row r="82" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A82" s="5"/>
       <c r="B82" s="5"/>
       <c r="C82" s="5"/>
@@ -9796,7 +9818,7 @@
       <c r="AD82" s="5"/>
       <c r="AE82" s="5"/>
     </row>
-    <row r="83" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A83" s="5"/>
       <c r="B83" s="5"/>
       <c r="C83" s="5"/>
@@ -9829,7 +9851,7 @@
       <c r="AD83" s="5"/>
       <c r="AE83" s="5"/>
     </row>
-    <row r="84" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A84" s="5"/>
       <c r="B84" s="5"/>
       <c r="C84" s="5"/>
@@ -9862,7 +9884,7 @@
       <c r="AD84" s="5"/>
       <c r="AE84" s="5"/>
     </row>
-    <row r="85" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A85" s="5"/>
       <c r="B85" s="5"/>
       <c r="C85" s="5"/>
@@ -9895,7 +9917,7 @@
       <c r="AD85" s="5"/>
       <c r="AE85" s="5"/>
     </row>
-    <row r="86" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:31" ht="15" x14ac:dyDescent="0.2">
       <c r="A86" s="5"/>
       <c r="B86" s="5"/>
       <c r="C86" s="5"/>
@@ -40058,7 +40080,11 @@
       <c r="AE999" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O62" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:O62" xr:uid="{00000000-0009-0000-0000-000001000000}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:O62">
+      <sortCondition ref="C1:C62"/>
+    </sortState>
+  </autoFilter>
   <phoneticPr fontId="9" type="noConversion"/>
   <pageMargins left="0" right="0" top="0" bottom="0" header="0" footer="0"/>
 </worksheet>
@@ -40089,7 +40115,7 @@
         <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>47</v>
@@ -40109,13 +40135,13 @@
         <v>244</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>417</v>
+        <v>412</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>418</v>
+        <v>413</v>
       </c>
     </row>
     <row r="3" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40129,13 +40155,13 @@
         <v>302</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>419</v>
+        <v>414</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40149,13 +40175,13 @@
         <v>106</v>
       </c>
       <c r="D4" s="5" t="s">
+        <v>411</v>
+      </c>
+      <c r="E4" s="9" t="s">
         <v>416</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>421</v>
-      </c>
       <c r="F4" s="9" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
     </row>
     <row r="5" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40169,13 +40195,13 @@
         <v>206</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>424</v>
+        <v>419</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40189,13 +40215,13 @@
         <v>251</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>425</v>
+        <v>420</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>426</v>
+        <v>421</v>
       </c>
     </row>
     <row r="7" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40209,13 +40235,13 @@
         <v>212</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40229,13 +40255,13 @@
         <v>218</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="9" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40249,13 +40275,13 @@
         <v>309</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40269,13 +40295,13 @@
         <v>316</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="11" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40289,13 +40315,13 @@
         <v>238</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40309,13 +40335,13 @@
         <v>181</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40329,13 +40355,13 @@
         <v>258</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F13" s="9" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40349,13 +40375,13 @@
         <v>168</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F14" s="9" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40369,13 +40395,13 @@
         <v>322</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F15" s="9" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40389,13 +40415,13 @@
         <v>283</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F16" s="9" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40409,13 +40435,13 @@
         <v>188</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F17" s="9" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40429,13 +40455,13 @@
         <v>67</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F18" s="9" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40449,13 +40475,13 @@
         <v>264</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F19" s="9" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="15" x14ac:dyDescent="0.2">
@@ -40469,13 +40495,13 @@
         <v>194</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F20" s="9" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40489,13 +40515,13 @@
         <v>135</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
     </row>
     <row r="22" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40509,13 +40535,13 @@
         <v>75</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F22" s="9" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="23" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40529,13 +40555,13 @@
         <v>117</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F23" s="9" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40549,13 +40575,13 @@
         <v>123</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E24" s="9" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F24" s="9" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40569,13 +40595,13 @@
         <v>174</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E25" s="9" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F25" s="9" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40589,13 +40615,13 @@
         <v>129</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E26" s="9" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F26" s="9" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40609,13 +40635,13 @@
         <v>200</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F27" s="9" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40629,13 +40655,13 @@
         <v>149</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E28" s="9" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F28" s="9" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40649,13 +40675,13 @@
         <v>93</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E29" s="9" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F29" s="9" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40669,13 +40695,13 @@
         <v>290</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F30" s="9" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40689,13 +40715,13 @@
         <v>296</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E31" s="9" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40709,13 +40735,13 @@
         <v>270</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E32" s="9" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F32" s="9" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40729,13 +40755,13 @@
         <v>156</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E33" s="9" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F33" s="9" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="34" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40749,13 +40775,13 @@
         <v>81</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F34" s="9" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40769,13 +40795,13 @@
         <v>99</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F35" s="9" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
     </row>
     <row r="36" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40789,13 +40815,13 @@
         <v>328</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E36" s="9" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F36" s="9" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
     </row>
     <row r="37" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40809,13 +40835,13 @@
         <v>87</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E37" s="9" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F37" s="9" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40829,13 +40855,13 @@
         <v>162</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E38" s="9" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F38" s="9" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -40849,13 +40875,13 @@
         <v>276</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
       <c r="E39" s="9" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F39" s="9" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44769,7 +44795,7 @@
         <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>54</v>
@@ -44786,10 +44812,10 @@
         <v>244</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15" x14ac:dyDescent="0.2">
@@ -44803,10 +44829,10 @@
         <v>302</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15" x14ac:dyDescent="0.2">
@@ -44820,10 +44846,10 @@
         <v>106</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15" x14ac:dyDescent="0.2">
@@ -44837,10 +44863,10 @@
         <v>141</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44854,10 +44880,10 @@
         <v>309</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>494</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>499</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44871,10 +44897,10 @@
         <v>238</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44888,10 +44914,10 @@
         <v>232</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44905,10 +44931,10 @@
         <v>168</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44922,10 +44948,10 @@
         <v>225</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E10" s="16" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F10" s="11"/>
       <c r="G10" s="11"/>
@@ -44954,10 +44980,10 @@
         <v>322</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44971,10 +44997,10 @@
         <v>283</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -44988,10 +45014,10 @@
         <v>188</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45005,10 +45031,10 @@
         <v>264</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45022,10 +45048,10 @@
         <v>135</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45039,10 +45065,10 @@
         <v>117</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45056,10 +45082,10 @@
         <v>123</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45073,10 +45099,10 @@
         <v>174</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45090,10 +45116,10 @@
         <v>129</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45107,10 +45133,10 @@
         <v>290</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45124,10 +45150,10 @@
         <v>270</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E21" s="9" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45141,10 +45167,10 @@
         <v>156</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -45152,16 +45178,16 @@
         <v>333</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C23" s="5" t="s">
         <v>335</v>
       </c>
+      <c r="C23" s="17" t="s">
+        <v>531</v>
+      </c>
       <c r="D23" s="5" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E23" s="12" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49021,7 +49047,7 @@
         <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>58</v>
@@ -49038,10 +49064,10 @@
         <v>106</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49055,10 +49081,10 @@
         <v>135</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49072,10 +49098,10 @@
         <v>168</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49089,10 +49115,10 @@
         <v>174</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49106,10 +49132,10 @@
         <v>188</v>
       </c>
       <c r="D6" s="5" t="s">
+        <v>513</v>
+      </c>
+      <c r="E6" s="9" t="s">
         <v>518</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>523</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49123,10 +49149,10 @@
         <v>258</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49140,10 +49166,10 @@
         <v>270</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49157,10 +49183,10 @@
         <v>283</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -49174,10 +49200,10 @@
         <v>328</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -49191,10 +49217,10 @@
         <v>309</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E11" s="14" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="F11" s="15"/>
       <c r="G11" s="15"/>
@@ -49223,10 +49249,10 @@
         <v>244</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F12" s="15"/>
       <c r="G12" s="15"/>
@@ -49255,10 +49281,10 @@
         <v>238</v>
       </c>
       <c r="D13" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F13" s="15"/>
       <c r="G13" s="15"/>
@@ -49287,10 +49313,10 @@
         <v>290</v>
       </c>
       <c r="D14" s="13" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="F14" s="15"/>
       <c r="G14" s="15"/>
@@ -53140,7 +53166,7 @@
         <v>42</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E1" s="5" t="s">
         <v>61</v>
@@ -53157,10 +53183,10 @@
         <v>106</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>421</v>
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -53174,10 +53200,10 @@
         <v>206</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>423</v>
+        <v>418</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -53191,10 +53217,10 @@
         <v>117</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E4" s="9" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -53208,10 +53234,10 @@
         <v>129</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -53225,10 +53251,10 @@
         <v>81</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -59899,26 +59925,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="4f4ed000-4b05-45b9-8673-b0d9b7fd1bfe" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a87903cd-e438-4fee-a472-85f26478213c">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100F4EC71C42C1053418F50398D2AFBB372" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="55163095b73f34bc10957ca2f6304bd7">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a87903cd-e438-4fee-a472-85f26478213c" xmlns:ns3="4f4ed000-4b05-45b9-8673-b0d9b7fd1bfe" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8365bd8fc5a0e2516c2aaec202d2f09e" ns2:_="" ns3:_="">
     <xsd:import namespace="a87903cd-e438-4fee-a472-85f26478213c"/>
@@ -60153,10 +60159,41 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="4f4ed000-4b05-45b9-8673-b0d9b7fd1bfe" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a87903cd-e438-4fee-a472-85f26478213c">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC17C425-7B25-4950-B9D0-562BEFD3161E}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD394625-589F-463E-9198-C506371B4AE2}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a87903cd-e438-4fee-a472-85f26478213c"/>
+    <ds:schemaRef ds:uri="4f4ed000-4b05-45b9-8673-b0d9b7fd1bfe"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -60173,20 +60210,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FD394625-589F-463E-9198-C506371B4AE2}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FC17C425-7B25-4950-B9D0-562BEFD3161E}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="a87903cd-e438-4fee-a472-85f26478213c"/>
-    <ds:schemaRef ds:uri="4f4ed000-4b05-45b9-8673-b0d9b7fd1bfe"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>